--- a/DADOS_CONTRATOS.xlsx
+++ b/DADOS_CONTRATOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcos.brumatti\Documents\GitHub\patrimonio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{777498D0-5D8D-4358-BDEA-417C41E012AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C77C610-E881-4DAA-9674-89C566D3F9FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="295">
   <si>
     <t>id</t>
   </si>
@@ -894,7 +894,25 @@
     <t>OPERAÇÃO, MANUTENÇÃO E CONSERVAÇÃO DO SISTEMA PÚBLICO DE ABASTECIMENTO DE ÁGUA DO MUNICÍPIO DE RONDONÓPOLIS - MT</t>
   </si>
   <si>
+    <t>023/2026</t>
+  </si>
+  <si>
+    <t>CONSORCIO APOIO HOUER MVIANA</t>
+  </si>
+  <si>
+    <t>SERVIÇOS DE APOIO TÉCNICO, ECONÔMICO E FINANCEIRO, ELABORAÇÃO E ESTRUTURAÇÃO DE PROCESSOS, ANÁLISE TÉCNICO-JURÍDICA E GERENCIAMENTO DE PROJETOS PARA GESTÃO PÚBLICA</t>
+  </si>
+  <si>
     <t>019/2026</t>
+  </si>
+  <si>
+    <t>DIM BEL CONSTRUTORA, EQUIPAMENTOS E SERVIÇOS LTDA</t>
+  </si>
+  <si>
+    <t>EXECUÇÃO DAS INTERLIGAÇÕES E CAIXAS HIDRÁULICAS DAS ESTAÇÕES DE TRATAMENTO DE ÁGUA 1 E 2 COM O RESERVATÓRIO E ELEVATÓRIAS DE ÁGUA TRATADA NA ESTAÇÃO DE TRATAMENTO DE ÁGUA (ETA).</t>
+  </si>
+  <si>
+    <t>CE 006/2026</t>
   </si>
 </sst>
 </file>
@@ -1373,7 +1391,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Planilha1"/>
-  <dimension ref="A1:P60"/>
+  <dimension ref="A1:P61"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.28515625" customWidth="1"/>
@@ -1462,7 +1480,7 @@
         <v>45064</v>
       </c>
       <c r="G2" s="4">
-        <f t="shared" ref="G2:G59" si="0">F2-E2</f>
+        <f t="shared" ref="G2:G61" si="0">F2-E2</f>
         <v>379</v>
       </c>
       <c r="H2" s="17">
@@ -3972,12 +3990,82 @@
         <v>46104</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
         <v>288</v>
       </c>
       <c r="C60" t="s">
-        <v>156</v>
+        <v>289</v>
+      </c>
+      <c r="D60" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="E60" s="1">
+        <v>46241</v>
+      </c>
+      <c r="F60" s="1">
+        <v>46605</v>
+      </c>
+      <c r="G60">
+        <f t="shared" si="0"/>
+        <v>364</v>
+      </c>
+      <c r="H60" s="30">
+        <v>3000075</v>
+      </c>
+      <c r="I60" t="s">
+        <v>91</v>
+      </c>
+      <c r="J60" t="s">
+        <v>19</v>
+      </c>
+      <c r="K60" t="s">
+        <v>20</v>
+      </c>
+      <c r="L60">
+        <v>24</v>
+      </c>
+      <c r="M60" s="1">
+        <v>46248</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+      <c r="B61" t="s">
+        <v>291</v>
+      </c>
+      <c r="C61" t="s">
+        <v>292</v>
+      </c>
+      <c r="D61" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="E61" s="1">
+        <v>46225</v>
+      </c>
+      <c r="F61" s="1">
+        <v>46589</v>
+      </c>
+      <c r="G61">
+        <f t="shared" si="0"/>
+        <v>364</v>
+      </c>
+      <c r="H61" s="30">
+        <v>570000</v>
+      </c>
+      <c r="I61" t="s">
+        <v>294</v>
+      </c>
+      <c r="J61" t="s">
+        <v>19</v>
+      </c>
+      <c r="K61" t="s">
+        <v>20</v>
+      </c>
+      <c r="L61">
+        <v>20</v>
+      </c>
+      <c r="M61" s="1">
+        <v>46233</v>
       </c>
     </row>
   </sheetData>
@@ -4282,7 +4370,7 @@
       <c r="C23" s="1"/>
       <c r="D23" s="1">
         <f ca="1">TODAY()</f>
-        <v>46231</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -4313,7 +4401,7 @@
       </c>
       <c r="D26" s="1">
         <f ca="1">TODAY()</f>
-        <v>46231</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
